--- a/data/source_data/corrected_source_data.xlsx
+++ b/data/source_data/corrected_source_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6189F32-2D01-415F-B9F2-8498D400655B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{996B8954-3A4D-40A5-8B62-F163336DBE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="7" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1367" uniqueCount="717">
   <si>
     <t>A_A</t>
   </si>
@@ -2030,9 +2030,6 @@
   </si>
   <si>
     <t>e</t>
-  </si>
-  <si>
-    <t>xgboost</t>
   </si>
   <si>
     <t>PR-AUC Results</t>
@@ -2570,12 +2567,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
@@ -2596,18 +2593,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C2" t="s">
         <v>679</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -4412,7 +4409,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.3">
@@ -8938,30 +8935,30 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE98C822-9AFF-41DB-8568-39888AAB8CBA}">
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:M39"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
@@ -9000,7 +8997,7 @@
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C5" s="4">
         <v>0.98495536447638898</v>
@@ -9015,7 +9012,7 @@
         <v>0.97630229964370896</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="J5" s="4">
         <v>0.69375544833674796</v>
@@ -9033,7 +9030,7 @@
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C6" s="4">
         <v>0.77644994125607703</v>
@@ -9048,7 +9045,7 @@
         <v>0.74622594279257304</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="J6" s="4">
         <v>0.26558807452050498</v>
@@ -9066,7 +9063,7 @@
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C7" s="4">
         <v>0.95995838037918801</v>
@@ -9081,7 +9078,7 @@
         <v>0.82704635148070904</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="J7" s="4">
         <v>0.45447584762287102</v>
@@ -9099,7 +9096,7 @@
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C8" s="4">
         <v>0.85184744586748595</v>
@@ -9114,7 +9111,7 @@
         <v>0.84594402449756301</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="J8" s="4">
         <v>0.17371010953383001</v>
@@ -9132,7 +9129,7 @@
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C9" s="4">
         <v>0.93542321879938495</v>
@@ -9147,7 +9144,7 @@
         <v>0.69590739713377503</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="J9" s="4">
         <v>0.38879058408051897</v>
@@ -9165,7 +9162,7 @@
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="C10" s="4">
         <v>0.65872149745182695</v>
@@ -9180,7 +9177,7 @@
         <v>0.56604317329785003</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="J10" s="4">
         <v>0.18834281718756099</v>
@@ -9198,7 +9195,7 @@
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C11" s="4">
         <v>0.80981566813231498</v>
@@ -9213,7 +9210,7 @@
         <v>0.61983711230854999</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="J11" s="4">
         <v>0.16462898897196601</v>
@@ -9231,7 +9228,7 @@
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C12" s="4">
         <v>0.67468568872046397</v>
@@ -9246,7 +9243,7 @@
         <v>0.65938705636133899</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="J12" s="4">
         <v>4.8560788604636897E-2</v>
@@ -9272,207 +9269,233 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
-        <v>665</v>
-      </c>
-      <c r="I17" t="s">
-        <v>664</v>
+        <v>707</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="C19" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D19" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E19" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F19" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="J19" t="s">
+      <c r="I19" s="2"/>
+      <c r="J19" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="K19" t="s">
+      <c r="K19" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="L19" t="s">
+      <c r="L19" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="M19" t="s">
+      <c r="M19" s="2" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C20" s="6">
+        <v>0.96054600247461297</v>
+      </c>
+      <c r="D20" s="6">
+        <v>0.87299008415111301</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.85663577393013302</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.53770210075037495</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="J20" s="6">
+        <v>0.439556051245174</v>
+      </c>
+      <c r="K20" s="6">
+        <v>0.21290271965699401</v>
+      </c>
+      <c r="L20" s="6">
+        <v>0.12204008204615401</v>
+      </c>
+      <c r="M20" s="6">
+        <v>1.8528070994233502E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B21" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="C20">
-        <v>0.98515589713910301</v>
-      </c>
-      <c r="D20">
-        <v>0.95954323099961902</v>
-      </c>
-      <c r="E20">
-        <v>0.98102169304064601</v>
-      </c>
-      <c r="F20">
-        <v>0.97579066983731699</v>
-      </c>
-      <c r="I20" t="s">
+      <c r="C21" s="6">
+        <v>0.90695330966097998</v>
+      </c>
+      <c r="D21" s="6">
+        <v>0.82856827179551096</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.82160253494877999</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.53880628532854602</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>669</v>
       </c>
-      <c r="J20">
-        <v>0.69790071435703005</v>
-      </c>
-      <c r="K20">
-        <v>0.475575527832304</v>
-      </c>
-      <c r="L20">
-        <v>0.63358677452742695</v>
-      </c>
-      <c r="M20">
-        <v>0.60688756251547105</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B21" t="s">
+      <c r="J21" s="6">
+        <v>0.26865283588532501</v>
+      </c>
+      <c r="K21" s="6">
+        <v>0.14713853907636501</v>
+      </c>
+      <c r="L21" s="6">
+        <v>0.11683558601466</v>
+      </c>
+      <c r="M21" s="6">
+        <v>1.7691546039403299E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B22" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="C21">
-        <v>0.96337866637551495</v>
-      </c>
-      <c r="D21">
-        <v>0.90796720274878595</v>
-      </c>
-      <c r="E21">
-        <v>0.95540192439016602</v>
-      </c>
-      <c r="F21">
-        <v>0.82225396231844605</v>
-      </c>
-      <c r="I21" t="s">
+      <c r="C22" s="6">
+        <v>0.59235388003754197</v>
+      </c>
+      <c r="D22" s="6">
+        <v>0.71971199355846305</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.95988974107205005</v>
+      </c>
+      <c r="F22" s="6">
+        <v>0.95474978483477102</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="J21">
-        <v>0.482971358802813</v>
-      </c>
-      <c r="K21">
-        <v>0.28441166454225703</v>
-      </c>
-      <c r="L21">
-        <v>0.42379710576079999</v>
-      </c>
-      <c r="M21">
-        <v>9.8555108174370701E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B22" t="s">
+      <c r="J22" s="6">
+        <v>9.16200977958362E-2</v>
+      </c>
+      <c r="K22" s="6">
+        <v>0.13427451234436899</v>
+      </c>
+      <c r="L22" s="6">
+        <v>0.44061637493975198</v>
+      </c>
+      <c r="M22" s="6">
+        <v>0.42087856150882003</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B23" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="C22">
-        <v>0.98475483181367596</v>
-      </c>
-      <c r="D22">
-        <v>0.97266755739527699</v>
-      </c>
-      <c r="E22">
-        <v>0.97504837042248405</v>
-      </c>
-      <c r="F22">
-        <v>0.97681392945010204</v>
-      </c>
-      <c r="I22" t="s">
+      <c r="C23" s="6">
+        <v>0.41048968524267399</v>
+      </c>
+      <c r="D23" s="6">
+        <v>0.41698000171772298</v>
+      </c>
+      <c r="E23" s="6">
+        <v>0.72425322901950195</v>
+      </c>
+      <c r="F23" s="6">
+        <v>0.59328006126715405</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="J22">
-        <v>0.68961018231646598</v>
-      </c>
-      <c r="K22">
-        <v>0.56907756599047199</v>
-      </c>
-      <c r="L22">
-        <v>0.56581395202848195</v>
-      </c>
-      <c r="M22">
-        <v>0.60136585960060596</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B23" t="s">
-        <v>672</v>
-      </c>
-      <c r="C23">
-        <v>0.90746777122325495</v>
-      </c>
-      <c r="D23">
-        <v>0.88109512472960305</v>
-      </c>
-      <c r="E23">
-        <v>0.86566404678098396</v>
-      </c>
-      <c r="F23">
-        <v>0.56956083194910401</v>
-      </c>
-      <c r="I23" t="s">
-        <v>672</v>
-      </c>
-      <c r="J23">
-        <v>0.29460980935822501</v>
-      </c>
-      <c r="K23">
-        <v>0.21029008778747299</v>
-      </c>
-      <c r="L23">
-        <v>0.134819496495555</v>
-      </c>
-      <c r="M23">
-        <v>1.9437027526535099E-2</v>
+      <c r="J23" s="6">
+        <v>0.10803279848979599</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1.13065081312949E-2</v>
+      </c>
+      <c r="L23" s="6">
+        <v>6.86762787914873E-2</v>
+      </c>
+      <c r="M23" s="6">
+        <v>1.5989554847513899E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>666</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>666</v>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B28" s="2"/>
-      <c r="C28" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="L28" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>266</v>
+      <c r="B28" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C28" s="6">
+        <v>0.96398423947860301</v>
+      </c>
+      <c r="D28" s="6">
+        <v>0.92594068998304802</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.965049507355483</v>
+      </c>
+      <c r="F28" s="6">
+        <v>0.84077034608477796</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="J28" s="6">
+        <v>0.224582192217708</v>
+      </c>
+      <c r="K28" s="6">
+        <v>0.36033861686250401</v>
+      </c>
+      <c r="L28" s="6">
+        <v>0.204717701780355</v>
+      </c>
+      <c r="M28" s="6">
+        <v>0.19391046927535999</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
@@ -9480,31 +9503,31 @@
         <v>669</v>
       </c>
       <c r="C29" s="6">
-        <v>0.96054600247461297</v>
+        <v>0.90803141123790798</v>
       </c>
       <c r="D29" s="6">
-        <v>0.87299008415111301</v>
+        <v>0.91485085329439897</v>
       </c>
       <c r="E29" s="6">
-        <v>0.85663577393013302</v>
+        <v>0.90397201138421202</v>
       </c>
       <c r="F29" s="6">
-        <v>0.53770210075037495</v>
+        <v>0.72103045111833497</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>669</v>
       </c>
       <c r="J29" s="6">
-        <v>0.439556051245174</v>
+        <v>7.6938330383421294E-2</v>
       </c>
       <c r="K29" s="6">
-        <v>0.21290271965699401</v>
+        <v>0.29259230033050299</v>
       </c>
       <c r="L29" s="6">
-        <v>0.12204008204615401</v>
+        <v>9.3402311073730801E-2</v>
       </c>
       <c r="M29" s="6">
-        <v>1.8528070994233502E-2</v>
+        <v>7.3797106203985594E-2</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.3">
@@ -9512,31 +9535,31 @@
         <v>670</v>
       </c>
       <c r="C30" s="6">
-        <v>0.90695330966097998</v>
+        <v>0.95593252127977402</v>
       </c>
       <c r="D30" s="6">
-        <v>0.82856827179551096</v>
+        <v>0.94533420393984002</v>
       </c>
       <c r="E30" s="6">
-        <v>0.82160253494877999</v>
+        <v>0.96325752819959298</v>
       </c>
       <c r="F30" s="6">
-        <v>0.53880628532854602</v>
+        <v>0.81332235687664001</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>670</v>
       </c>
       <c r="J30" s="6">
-        <v>0.26865283588532501</v>
+        <v>0.122838026849951</v>
       </c>
       <c r="K30" s="6">
-        <v>0.14713853907636501</v>
+        <v>0.37251372595834997</v>
       </c>
       <c r="L30" s="6">
-        <v>0.11683558601466</v>
+        <v>0.122838026849951</v>
       </c>
       <c r="M30" s="6">
-        <v>1.7691546039403299E-2</v>
+        <v>0.122838026849951</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
@@ -9544,96 +9567,96 @@
         <v>671</v>
       </c>
       <c r="C31" s="6">
-        <v>0.59235388003754197</v>
+        <v>0.71159992502672298</v>
       </c>
       <c r="D31" s="6">
-        <v>0.71971199355846305</v>
+        <v>0.90618276773144102</v>
       </c>
       <c r="E31" s="6">
-        <v>0.95988974107205005</v>
+        <v>0.77432366135277297</v>
       </c>
       <c r="F31" s="6">
-        <v>0.95474978483477102</v>
+        <v>0.518643773498765</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>671</v>
       </c>
       <c r="J31" s="6">
-        <v>9.16200977958362E-2</v>
+        <v>2.0183246825852499E-2</v>
       </c>
       <c r="K31" s="6">
-        <v>0.13427451234436899</v>
+        <v>0.22313080625564299</v>
       </c>
       <c r="L31" s="6">
-        <v>0.44061637493975198</v>
+        <v>2.0183246825852499E-2</v>
       </c>
       <c r="M31" s="6">
-        <v>0.42087856150882003</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B32" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C32" s="6">
-        <v>0.41048968524267399</v>
-      </c>
-      <c r="D32" s="6">
-        <v>0.41698000171772298</v>
-      </c>
-      <c r="E32" s="6">
-        <v>0.72425322901950195</v>
-      </c>
-      <c r="F32" s="6">
-        <v>0.59328006126715405</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="J32" s="6">
-        <v>0.10803279848979599</v>
-      </c>
-      <c r="K32" s="6">
-        <v>1.13065081312949E-2</v>
-      </c>
-      <c r="L32" s="6">
-        <v>6.86762787914873E-2</v>
-      </c>
-      <c r="M32" s="6">
-        <v>1.5989554847513899E-2</v>
+        <v>2.0183246825852499E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>667</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>667</v>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B36" s="2"/>
-      <c r="C36" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I36" s="2"/>
-      <c r="J36" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="L36" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M36" s="2" t="s">
-        <v>266</v>
+      <c r="B36" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="C36" s="6">
+        <v>0.88352217416994905</v>
+      </c>
+      <c r="D36" s="6">
+        <v>0.94027882349884595</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.87459448410920004</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.87171533143010305</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="J36" s="6">
+        <v>0.224582192217708</v>
+      </c>
+      <c r="K36" s="6">
+        <v>0.36033861686250401</v>
+      </c>
+      <c r="L36" s="6">
+        <v>0.204717701780355</v>
+      </c>
+      <c r="M36" s="6">
+        <v>0.19391046927535999</v>
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
@@ -9641,31 +9664,31 @@
         <v>669</v>
       </c>
       <c r="C37" s="6">
-        <v>0.96398423947860301</v>
+        <v>0.77882343668821297</v>
       </c>
       <c r="D37" s="6">
-        <v>0.92594068998304802</v>
+        <v>0.92276842120880997</v>
       </c>
       <c r="E37" s="6">
-        <v>0.965049507355483</v>
+        <v>0.79148126187306</v>
       </c>
       <c r="F37" s="6">
-        <v>0.84077034608477796</v>
+        <v>0.74822617196996499</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>669</v>
       </c>
       <c r="J37" s="6">
-        <v>0.224582192217708</v>
+        <v>7.6938330383421294E-2</v>
       </c>
       <c r="K37" s="6">
-        <v>0.36033861686250401</v>
+        <v>0.29259230033050299</v>
       </c>
       <c r="L37" s="6">
-        <v>0.204717701780355</v>
+        <v>9.3402311073730801E-2</v>
       </c>
       <c r="M37" s="6">
-        <v>0.19391046927535999</v>
+        <v>7.3797106203985594E-2</v>
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
@@ -9673,31 +9696,31 @@
         <v>670</v>
       </c>
       <c r="C38" s="6">
-        <v>0.90803141123790798</v>
+        <v>0.82017271756502297</v>
       </c>
       <c r="D38" s="6">
-        <v>0.91485085329439897</v>
+        <v>0.94526729489900596</v>
       </c>
       <c r="E38" s="6">
-        <v>0.90397201138421202</v>
+        <v>0.82017271756502297</v>
       </c>
       <c r="F38" s="6">
-        <v>0.72103045111833497</v>
+        <v>0.82017271756502297</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>670</v>
       </c>
       <c r="J38" s="6">
-        <v>7.6938330383421294E-2</v>
+        <v>0.122838026849951</v>
       </c>
       <c r="K38" s="6">
-        <v>0.29259230033050299</v>
+        <v>0.37251372595834997</v>
       </c>
       <c r="L38" s="6">
-        <v>9.3402311073730801E-2</v>
+        <v>0.122838026849951</v>
       </c>
       <c r="M38" s="6">
-        <v>7.3797106203985594E-2</v>
+        <v>0.122838026849951</v>
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
@@ -9705,223 +9728,30 @@
         <v>671</v>
       </c>
       <c r="C39" s="6">
-        <v>0.95593252127977402</v>
+        <v>0.57054794075271398</v>
       </c>
       <c r="D39" s="6">
-        <v>0.94533420393984002</v>
+        <v>0.855178596352686</v>
       </c>
       <c r="E39" s="6">
-        <v>0.96325752819959298</v>
+        <v>0.57054794075271398</v>
       </c>
       <c r="F39" s="6">
-        <v>0.81332235687664001</v>
+        <v>0.57054794075271398</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>671</v>
       </c>
       <c r="J39" s="6">
-        <v>0.122838026849951</v>
+        <v>2.0183246825852499E-2</v>
       </c>
       <c r="K39" s="6">
-        <v>0.37251372595834997</v>
+        <v>0.22313080625564299</v>
       </c>
       <c r="L39" s="6">
-        <v>0.122838026849951</v>
+        <v>2.0183246825852499E-2</v>
       </c>
       <c r="M39" s="6">
-        <v>0.122838026849951</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B40" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C40" s="6">
-        <v>0.71159992502672298</v>
-      </c>
-      <c r="D40" s="6">
-        <v>0.90618276773144102</v>
-      </c>
-      <c r="E40" s="6">
-        <v>0.77432366135277297</v>
-      </c>
-      <c r="F40" s="6">
-        <v>0.518643773498765</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="J40" s="6">
-        <v>2.0183246825852499E-2</v>
-      </c>
-      <c r="K40" s="6">
-        <v>0.22313080625564299</v>
-      </c>
-      <c r="L40" s="6">
-        <v>2.0183246825852499E-2</v>
-      </c>
-      <c r="M40" s="6">
-        <v>2.0183246825852499E-2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B44" s="2"/>
-      <c r="C44" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="L44" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="M44" s="2" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B45" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="C45" s="6">
-        <v>0.88352217416994905</v>
-      </c>
-      <c r="D45" s="6">
-        <v>0.94027882349884595</v>
-      </c>
-      <c r="E45" s="6">
-        <v>0.87459448410920004</v>
-      </c>
-      <c r="F45" s="6">
-        <v>0.87171533143010305</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>669</v>
-      </c>
-      <c r="J45" s="6">
-        <v>0.224582192217708</v>
-      </c>
-      <c r="K45" s="6">
-        <v>0.36033861686250401</v>
-      </c>
-      <c r="L45" s="6">
-        <v>0.204717701780355</v>
-      </c>
-      <c r="M45" s="6">
-        <v>0.19391046927535999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B46" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C46" s="6">
-        <v>0.77882343668821297</v>
-      </c>
-      <c r="D46" s="6">
-        <v>0.92276842120880997</v>
-      </c>
-      <c r="E46" s="6">
-        <v>0.79148126187306</v>
-      </c>
-      <c r="F46" s="6">
-        <v>0.74822617196996499</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="J46" s="6">
-        <v>7.6938330383421294E-2</v>
-      </c>
-      <c r="K46" s="6">
-        <v>0.29259230033050299</v>
-      </c>
-      <c r="L46" s="6">
-        <v>9.3402311073730801E-2</v>
-      </c>
-      <c r="M46" s="6">
-        <v>7.3797106203985594E-2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B47" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="C47" s="6">
-        <v>0.82017271756502297</v>
-      </c>
-      <c r="D47" s="6">
-        <v>0.94526729489900596</v>
-      </c>
-      <c r="E47" s="6">
-        <v>0.82017271756502297</v>
-      </c>
-      <c r="F47" s="6">
-        <v>0.82017271756502297</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="J47" s="6">
-        <v>0.122838026849951</v>
-      </c>
-      <c r="K47" s="6">
-        <v>0.37251372595834997</v>
-      </c>
-      <c r="L47" s="6">
-        <v>0.122838026849951</v>
-      </c>
-      <c r="M47" s="6">
-        <v>0.122838026849951</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B48" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C48" s="6">
-        <v>0.57054794075271398</v>
-      </c>
-      <c r="D48" s="6">
-        <v>0.855178596352686</v>
-      </c>
-      <c r="E48" s="6">
-        <v>0.57054794075271398</v>
-      </c>
-      <c r="F48" s="6">
-        <v>0.57054794075271398</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="J48" s="6">
-        <v>2.0183246825852499E-2</v>
-      </c>
-      <c r="K48" s="6">
-        <v>0.22313080625564299</v>
-      </c>
-      <c r="L48" s="6">
-        <v>2.0183246825852499E-2</v>
-      </c>
-      <c r="M48" s="6">
         <v>2.0183246825852499E-2</v>
       </c>
     </row>
@@ -9939,7 +9769,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -10127,7 +9957,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -10350,7 +10180,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
@@ -10608,18 +10438,18 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>678</v>
+      </c>
+      <c r="C2" t="s">
         <v>679</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>680</v>
-      </c>
-      <c r="D2" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -25801,69 +25631,69 @@
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C2" t="s">
         <v>683</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>684</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>685</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>686</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>687</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>688</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>689</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>690</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>691</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>692</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>693</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>694</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>695</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>696</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>697</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>698</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>699</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>700</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>701</v>
-      </c>
-      <c r="U2" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
@@ -26919,7 +26749,7 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -27222,7 +27052,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
